--- a/etf_holdings/2026-10-08_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-08_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB9"/>
+  <dimension ref="A1:BV26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,250 +439,350 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>00981A_異動類型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>00981A_調整方向</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>00981A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>00981A_權重_今日</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>00981A_權重變化</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>00981A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>00981A_股數_今日</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>00981A_股數變化</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>00991A_異動類型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>00991A_調整方向</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>00991A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>00991A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>00991A_權重_昨日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>00991A_權重_今日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>00991A_權重變化</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>00991A_股數_昨日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>00991A_股數_今日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>00991A_股數變化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>00985A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00985A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00985A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00985A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00985A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00985A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00985A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00985A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00985A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00985A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>00992A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00992A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00992A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00992A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00992A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00992A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00992A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00992A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>00405A_異動類型</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>00405A_調整方向</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>00405A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>00405A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>00405A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>00405A_權重_今日</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>00405A_權重變化</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>00405A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>00405A_股數_今日</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>00405A_股數變化</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -691,12 +791,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -704,7 +804,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00400A,00405A,00993A</t>
+          <t>00985A,00991A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -717,62 +817,62 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4.57%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>5.60%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>+1.03%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>64300</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>79300</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6.71%</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6.31%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>-0.40%</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -780,109 +880,129 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>19600</v>
+        <v>67000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25600</v>
+        <v>50000</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2.70%</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>-1.07%</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>47400</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>28400</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-19,000</t>
-        </is>
-      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>5.93%</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-4.36%</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>128000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>-94,000</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00993A</t>
+          <t>00400A,00985A,00993A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -922,91 +1042,165 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>126000</v>
+        <v>56000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>59000</v>
+        <v>72000</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-67,000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>74000</v>
-      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-1.76%</t>
+        </is>
+      </c>
+      <c r="BJ3" t="n">
+        <v>39000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>-26,000</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>4.83%</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>-0.70%</t>
+        </is>
+      </c>
+      <c r="BT3" t="n">
+        <v>221000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>176000</v>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-45,000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00992A,00993A</t>
+          <t>00400A,00985A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1019,52 +1213,16 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>+0.83%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>275000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>422000</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>147,000</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -1087,22 +1245,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1111,14 +1269,14 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>14000</v>
+        <v>104000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22000</v>
+        <v>121000</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
@@ -1131,24 +1289,116 @@
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-1.44%</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>80000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>14000</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>-66,000</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="BT4" t="n">
+        <v>295000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>228000</v>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>-67,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00991A,00993A</t>
+          <t>00981A,00985A,00993A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1163,38 +1413,38 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1100000</v>
+        <v>9276000</v>
       </c>
       <c r="M5" t="n">
-        <v>1050000</v>
+        <v>8348000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>-928,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -1229,38 +1479,38 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>128000</v>
+        <v>605000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>34000</v>
+        <v>493000</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-94,000</t>
+          <t>-112,000</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
@@ -1273,24 +1523,80 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>+1.07%</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>87000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>153,000</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00992A,00993A</t>
+          <t>00400A,00403A,00993A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1303,90 +1609,72 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>1.26%</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1.84%</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>-1.02%</t>
-        </is>
-      </c>
-      <c r="AP6" t="n">
-        <v>344000</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>154000</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-190,000</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>95500</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>117500</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr"/>
@@ -1397,16 +1685,108 @@
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>+0.84%</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>19600</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>25600</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>2.70%</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-1.07%</t>
+        </is>
+      </c>
+      <c r="BT6" t="n">
+        <v>47400</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>28400</v>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1414,7 +1794,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00405A,00993A</t>
+          <t>00400A,00985A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1437,96 +1817,60 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>6.19%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>5.84%</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>183000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>173000</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-10,000</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>64000</v>
+        <v>28000</v>
       </c>
       <c r="AQ7" t="n">
-        <v>45000</v>
+        <v>39000</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-19,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
@@ -1539,16 +1883,72 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>4.66%</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="BT7" t="n">
+        <v>123000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>78000</v>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>-45,000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1556,7 +1956,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00400A,00993A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1596,101 +1996,121 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>2186000</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2684000</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>498,000</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>2.60%</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>0.84%</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>-1.76%</t>
-        </is>
-      </c>
-      <c r="AP8" t="n">
-        <v>39000</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>13000</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-26,000</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>4.83%</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4.13%</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>-0.70%</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>221000</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>176000</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-45,000</t>
-        </is>
-      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-0.72%</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1893000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>-548,000</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1698,7 +2118,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00400A,00993A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1743,86 +2163,2716 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>104000</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="n">
+        <v>105000</v>
+      </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2.39%</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>694000</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>609000</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-85,000</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="n">
+        <v>378000</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00400A,00993A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2.43%</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>126000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>59000</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>-67,000</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="n">
+        <v>74000</v>
+      </c>
+      <c r="BV11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00992A,00993A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>275000</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>422000</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>147,000</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
           <t>0.31%</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="AP9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
         <v>14000</v>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-66,000</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
+      <c r="BK12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>3420000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3741000</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>321,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>320000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>480000</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>160,000</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2.19%</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1.76%</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>-0.43%</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>295000</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>228000</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-67,000</t>
-        </is>
-      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>598000</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>406000</v>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-192,000</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>87000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>199000</v>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>112,000</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00992A,00993A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>344000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>154000</v>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>-190,000</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>132000</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>143000</v>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>5.73%</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>5.96%</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>165000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>176000</v>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00981A,00985A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8.61%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8.16%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>19300000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18721000</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-579,000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
+        </is>
+      </c>
+      <c r="AP17" t="n">
+        <v>268000</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>372000</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>104,000</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="AP18" t="n">
+        <v>136000</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>102000</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-34,000</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>18000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>41000</v>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="AP19" t="n">
+        <v>357000</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>278000</v>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-79,000</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="n">
+        <v>191000</v>
+      </c>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>616000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>684000</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>68,000</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>5.05%</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>-1.42%</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>64000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>45000</v>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>4.01%</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>-0.91%</t>
+        </is>
+      </c>
+      <c r="AP21" t="n">
+        <v>373000</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-73,000</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>+0.78%</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>58000</v>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>48,000</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00400A,00985A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="AP22" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>51000</v>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>+1.96%</t>
+        </is>
+      </c>
+      <c r="BT22" t="n">
+        <v>49000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>135,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="AP23" t="n">
+        <v>3926000</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4243000</v>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>317,000</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="n">
+        <v>259000</v>
+      </c>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="n">
+        <v>141000</v>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="n">
+        <v>110000</v>
+      </c>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>4.01%</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>+1.45%</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>155000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>244000</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>89,000</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00403A,00985A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>-0.71%</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>-800,000</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>1.41%</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="AP26" t="n">
+        <v>187000</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>167000</v>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
